--- a/data/trans_dic/P43E-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P43E-Edad-trans_dic.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>32,47%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>32,47%</t>
         </is>
       </c>
     </row>
@@ -635,32 +635,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>15,73; 28,84</t>
+          <t>15,84; 29,08</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,85; 22,02</t>
+          <t>10,77; 22,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18,23; 56,8</t>
+          <t>16,1; 53,35</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15,73; 28,84</t>
+          <t>15,84; 29,08</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>10,85; 22,02</t>
+          <t>10,77; 22,54</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,23; 56,8</t>
+          <t>16,1; 53,35</t>
         </is>
       </c>
     </row>
@@ -687,7 +687,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -702,7 +702,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>26,75%</t>
         </is>
       </c>
     </row>
@@ -715,32 +715,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>22,67; 31,32</t>
+          <t>22,72; 31,05</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>16,42; 25,09</t>
+          <t>16,73; 25,07</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,39; 29,29</t>
+          <t>19,71; 33,75</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22,67; 31,32</t>
+          <t>22,72; 31,05</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>16,42; 25,09</t>
+          <t>16,73; 25,07</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,39; 29,29</t>
+          <t>19,71; 33,75</t>
         </is>
       </c>
     </row>
@@ -767,7 +767,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>27,54%</t>
         </is>
       </c>
     </row>
@@ -795,32 +795,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>22,72; 30,59</t>
+          <t>22,48; 30,15</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>16,83; 23,83</t>
+          <t>16,63; 23,51</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>23,66; 32,81</t>
+          <t>23,17; 32,1</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>22,72; 30,59</t>
+          <t>22,48; 30,15</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>16,83; 23,83</t>
+          <t>16,63; 23,51</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23,66; 32,81</t>
+          <t>23,17; 32,1</t>
         </is>
       </c>
     </row>
@@ -847,7 +847,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>30,98%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>30,98%</t>
         </is>
       </c>
     </row>
@@ -875,32 +875,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>19,73; 28,92</t>
+          <t>20,13; 28,76</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11,98; 19,26</t>
+          <t>11,99; 19,09</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19,53; 32,01</t>
+          <t>27,36; 34,79</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19,73; 28,92</t>
+          <t>20,13; 28,76</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>11,98; 19,26</t>
+          <t>11,99; 19,09</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,53; 32,01</t>
+          <t>27,36; 34,79</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,2%</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>14,47; 24,36</t>
+          <t>14,04; 23,57</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>10,54; 19,03</t>
+          <t>10,12; 18,3</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18,82; 26,21</t>
+          <t>18,69; 26,19</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14,47; 24,36</t>
+          <t>14,04; 23,57</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>10,54; 19,03</t>
+          <t>10,12; 18,3</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,82; 26,21</t>
+          <t>18,69; 26,19</t>
         </is>
       </c>
     </row>
@@ -1007,7 +1007,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,29%</t>
         </is>
       </c>
     </row>
@@ -1035,32 +1035,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7,87; 18,12</t>
+          <t>7,78; 18,87</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8,01; 17,94</t>
+          <t>8,1; 17,94</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13,45; 21,18</t>
+          <t>13,81; 21,14</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7,87; 18,12</t>
+          <t>7,78; 18,87</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>8,01; 17,94</t>
+          <t>8,1; 17,94</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>13,45; 21,18</t>
+          <t>13,81; 21,14</t>
         </is>
       </c>
     </row>
@@ -1087,7 +1087,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,92%</t>
         </is>
       </c>
     </row>
@@ -1115,32 +1115,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7,73; 22,37</t>
+          <t>8,4; 23,5</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,57; 16,49</t>
+          <t>3,8; 15,74</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10,03; 18,44</t>
+          <t>10,44; 18,19</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7,73; 22,37</t>
+          <t>8,4; 23,5</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,57; 16,49</t>
+          <t>3,8; 15,74</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,03; 18,44</t>
+          <t>10,44; 18,19</t>
         </is>
       </c>
     </row>
@@ -1167,7 +1167,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>24,55%</t>
         </is>
       </c>
     </row>
@@ -1195,32 +1195,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>21,08; 24,84</t>
+          <t>21,27; 24,87</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>14,83; 17,99</t>
+          <t>14,8; 18,01</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>19,17; 25,19</t>
+          <t>22,7; 26,4</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>21,08; 24,84</t>
+          <t>21,27; 24,87</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>14,83; 17,99</t>
+          <t>14,8; 18,01</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,17; 25,19</t>
+          <t>22,7; 26,4</t>
         </is>
       </c>
     </row>
@@ -1395,7 +1395,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15668</t>
+          <t>15562</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1410,7 +1410,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15668</t>
+          <t>15562</t>
         </is>
       </c>
     </row>
@@ -1423,32 +1423,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>26173; 47987</t>
+          <t>26368; 48393</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>17379; 35268</t>
+          <t>17244; 36092</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7873; 24528</t>
+          <t>7714; 25569</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>26173; 47987</t>
+          <t>26368; 48393</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>17379; 35268</t>
+          <t>17244; 36092</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7873; 24528</t>
+          <t>7714; 25569</t>
         </is>
       </c>
     </row>
@@ -1513,7 +1513,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>46018</t>
+          <t>51235</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>46018</t>
+          <t>51235</t>
         </is>
       </c>
     </row>
@@ -1541,32 +1541,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>100056; 138245</t>
+          <t>100277; 137019</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>60338; 92213</t>
+          <t>61491; 92136</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>20539; 71742</t>
+          <t>37755; 64648</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>100056; 138245</t>
+          <t>100277; 137019</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>60338; 92213</t>
+          <t>61491; 92136</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>20539; 71742</t>
+          <t>37755; 64648</t>
         </is>
       </c>
     </row>
@@ -1631,7 +1631,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>71599</t>
+          <t>79806</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>71599</t>
+          <t>79806</t>
         </is>
       </c>
     </row>
@@ -1659,32 +1659,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>129239; 174061</t>
+          <t>127906; 171514</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>84316; 119386</t>
+          <t>83303; 117802</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>60545; 83953</t>
+          <t>67157; 93027</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>129239; 174061</t>
+          <t>127906; 171514</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>84316; 119386</t>
+          <t>83303; 117802</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>60545; 83953</t>
+          <t>67157; 93027</t>
         </is>
       </c>
     </row>
@@ -1749,7 +1749,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>108430</t>
+          <t>117955</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>108430</t>
+          <t>117955</t>
         </is>
       </c>
     </row>
@@ -1777,32 +1777,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>95205; 139547</t>
+          <t>97166; 138808</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>56585; 90953</t>
+          <t>56638; 90131</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>75823; 124261</t>
+          <t>104172; 132463</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>95205; 139547</t>
+          <t>97166; 138808</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>56585; 90953</t>
+          <t>56638; 90131</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>75823; 124261</t>
+          <t>104172; 132463</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>63086</t>
+          <t>69735</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>63086</t>
+          <t>69735</t>
         </is>
       </c>
     </row>
@@ -1895,32 +1895,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>44868; 75543</t>
+          <t>43522; 73096</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>33826; 61066</t>
+          <t>32484; 58724</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>53499; 74529</t>
+          <t>58691; 82278</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>44868; 75543</t>
+          <t>43522; 73096</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>33826; 61066</t>
+          <t>32484; 58724</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>53499; 74529</t>
+          <t>58691; 82278</t>
         </is>
       </c>
     </row>
@@ -1985,7 +1985,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>33765</t>
+          <t>37303</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2000,7 +2000,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>33765</t>
+          <t>37303</t>
         </is>
       </c>
     </row>
@@ -2013,32 +2013,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>14004; 32251</t>
+          <t>13856; 33599</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>16195; 36279</t>
+          <t>16374; 36286</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>26561; 41828</t>
+          <t>29792; 45591</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>14004; 32251</t>
+          <t>13856; 33599</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>16195; 36279</t>
+          <t>16374; 36286</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>26561; 41828</t>
+          <t>29792; 45591</t>
         </is>
       </c>
     </row>
@@ -2103,7 +2103,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>21444</t>
+          <t>23608</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2118,7 +2118,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>21444</t>
+          <t>23608</t>
         </is>
       </c>
     </row>
@@ -2131,32 +2131,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>7856; 22734</t>
+          <t>8538; 23886</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>4628; 21399</t>
+          <t>4928; 20422</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>15718; 28908</t>
+          <t>17716; 30850</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>7856; 22734</t>
+          <t>8538; 23886</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>4628; 21399</t>
+          <t>4928; 20422</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>15718; 28908</t>
+          <t>17716; 30850</t>
         </is>
       </c>
     </row>
@@ -2221,7 +2221,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>360010</t>
+          <t>395204</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>360010</t>
+          <t>395204</t>
         </is>
       </c>
     </row>
@@ -2249,32 +2249,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>474104; 558644</t>
+          <t>478474; 559306</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>319342; 387366</t>
+          <t>318740; 387912</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>301053; 395733</t>
+          <t>365309; 424889</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>474104; 558644</t>
+          <t>478474; 559306</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>319342; 387366</t>
+          <t>318740; 387912</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>301053; 395733</t>
+          <t>365309; 424889</t>
         </is>
       </c>
     </row>
